--- a/history_prices/MAR/prices_27022026.xlsx
+++ b/history_prices/MAR/prices_27022026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\MAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71D24CDD-6B37-47C3-B4AA-0513AF954F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5033493D-3A44-43DF-9704-3CCE4A781E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ЕКО БЮЛЕТИН" sheetId="1" r:id="rId1"/>
@@ -321,7 +321,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -340,6 +340,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -353,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -362,6 +368,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -665,18 +675,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.54296875" customWidth="1"/>
+    <col min="1" max="1" width="23.5703125" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="23.26953125" customWidth="1"/>
-    <col min="4" max="4" width="26.453125" customWidth="1"/>
-    <col min="5" max="5" width="23.26953125" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" customWidth="1"/>
+    <col min="5" max="5" width="23.28515625" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="18.54296875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -699,7 +709,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -718,7 +728,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -737,7 +747,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -756,7 +766,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -775,7 +785,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -794,7 +804,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -813,7 +823,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -832,7 +842,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -851,7 +861,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -870,7 +880,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -889,7 +899,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -908,7 +918,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -927,7 +937,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -946,7 +956,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -965,7 +975,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -984,7 +994,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -1003,7 +1013,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1022,7 +1032,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -1041,7 +1051,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -1060,7 +1070,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -1079,7 +1089,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1098,83 +1108,83 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="1">
-        <v>46080</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="B23" s="8">
+        <v>46080</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="3">
+      <c r="D23" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="11">
         <v>1.2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="1">
-        <v>46080</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="B24" s="8">
+        <v>46080</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="3">
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="11">
         <v>1.37</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="1">
-        <v>46080</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="B25" s="8">
+        <v>46080</v>
+      </c>
+      <c r="C25" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D25" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="3">
+      <c r="D25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="11">
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="1">
-        <v>46080</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="B26" s="8">
+        <v>46080</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="3">
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="11">
         <v>1.43</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>47</v>
       </c>
@@ -1193,7 +1203,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>49</v>
       </c>
@@ -1212,7 +1222,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>50</v>
       </c>
@@ -1231,7 +1241,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>52</v>
       </c>
@@ -1250,7 +1260,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>53</v>
       </c>
@@ -1269,7 +1279,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>55</v>
       </c>
@@ -1288,7 +1298,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1307,7 +1317,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>58</v>
       </c>
@@ -1326,7 +1336,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -1345,7 +1355,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>61</v>
       </c>
@@ -1364,7 +1374,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1383,7 +1393,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1402,7 +1412,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>66</v>
       </c>
@@ -1421,7 +1431,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>68</v>
       </c>
@@ -1440,7 +1450,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>69</v>
       </c>
@@ -1459,7 +1469,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>70</v>
       </c>
@@ -1478,7 +1488,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>71</v>
       </c>
@@ -1497,7 +1507,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>73</v>
       </c>
@@ -1516,7 +1526,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>74</v>
       </c>
@@ -1535,7 +1545,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>76</v>
       </c>
@@ -1554,7 +1564,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>77</v>
       </c>
@@ -1573,7 +1583,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>78</v>
       </c>
@@ -1592,7 +1602,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>79</v>
       </c>
@@ -1611,7 +1621,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>81</v>
       </c>
@@ -1630,7 +1640,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>82</v>
       </c>
@@ -1649,7 +1659,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>83</v>
       </c>
@@ -1668,7 +1678,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B53" s="1">
         <v>46080</v>
       </c>
@@ -1684,7 +1694,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B54" s="1">
         <v>46080</v>
       </c>
@@ -1700,7 +1710,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B55" s="1">
         <v>46080</v>
       </c>
@@ -1716,7 +1726,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B56" s="1">
         <v>46080</v>
       </c>
@@ -1732,7 +1742,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B57" s="1">
         <v>46080</v>
       </c>
@@ -1748,7 +1758,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B58" s="1">
         <v>46080</v>
       </c>
@@ -1764,7 +1774,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B59" s="1">
         <v>46080</v>
       </c>
@@ -1780,7 +1790,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B60" s="1">
         <v>46080</v>
       </c>
@@ -1796,7 +1806,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B61" s="1">
         <v>46080</v>
       </c>
@@ -1812,7 +1822,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B62" s="1">
         <v>46080</v>
       </c>
@@ -1828,7 +1838,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B63" s="1">
         <v>46080</v>
       </c>
@@ -1844,7 +1854,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B64" s="1">
         <v>46080</v>
       </c>
@@ -1860,7 +1870,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B65" s="1">
         <v>46080</v>
       </c>
@@ -1876,7 +1886,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B66" s="1">
         <v>46080</v>
       </c>
@@ -1892,7 +1902,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B67" s="1">
         <v>46080</v>
       </c>
@@ -1908,7 +1918,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B68" s="1">
         <v>46080</v>
       </c>
